--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107331</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982320</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73982320</v>
+        <v>126445080</v>
       </c>
       <c r="B2" t="n">
-        <v>107376</v>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hyltena. 600m VNV Hyltena, Sm</t>
+          <t>Rödjan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449730</v>
+        <v>449744</v>
       </c>
       <c r="R2" t="n">
-        <v>6391240</v>
+        <v>6391384</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1977-01-01</t>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E8a 4016. SOM: Arnica montana. LEG: Ragnar Lernedal</t>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,23 +775,236 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ängssnår</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Eduardo Prado</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Eduardo Prado, Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>73982320</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107907</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hyltena. 600m VNV Hyltena, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>449730</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6391240</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1977-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1977-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8a 4016. SOM: Arnica montana. LEG: Ragnar Lernedal</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ängssnår</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74782809</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hyltena. 600m VNV Hyltena, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>449730</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6391240</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1977-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1977-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8a 4016. SOM: Polygala vulgaris. LEG: Ragnar Lernedal</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ängssnår</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 70402-2021 artfynd.xlsx
+++ b/artfynd/A 70402-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126445080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982320</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>